--- a/output/2026-09-06_19_Slovenia_Primorsko-notranjska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-06_19_Slovenia_Primorsko-notranjska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Esistenza confermata (fonti: Bizi.si, AJPES, companywall.si, magro.si). Sede legale a Komen, unita' operativa (PE) a Vilharjeva cesta 24, 6250 Ilirska Bistrica. Trgovsko podjetje na debelo in drobno (azienda commerciale ingrosso/dettaglio): a Ilirska Bistrica vende materiale idraulico, elettrico, abbigliamento da lavoro e utensili; a Komen anche materiale edile, ferramenta e vernici; separata unita' 'Agro Trgovina' per prodotti agricoli. 13 dipendenti, fatturato 2024 circa 3,7 mln EUR. ATTENZIONE: e' una ferramenta/fornitura industriale generica (non specializzata in lavorazioni metalliche), ma vende utensili e materiale da officina a clientela professionale - da valutare idoneita' come canale distributivo.</t>
+          <t>Esistenza confermata (fonti: Bizi.si, AJPES, companywall.si, magro.si). Sede legale a Komen, unita' operativa (PE) a Vilharjeva cesta 24, 6250 Ilirska Bistrica. Trgovsko podjetje na debelo in drobno (azienda commerciale ingrosso/dettaglio): a Ilirska Bistrica vende materiale idraulico, elettrico, abbigliamento da lavoro e utensili; a Komen anche materiale edile, ferramenta e vernici; separata unita' 'Agro Trgovina' per prodotti agricoli. 13 dipendenti, fatturato 2024 circa 3,7 mln EUR. ATTENZIONE: e' una ferramenta/fornitura industriale generica (non specializzata in lavorazioni metalliche), ma vende utensili e materiale da officina a clientela professionale - da valutare idoneita' come canale distributivo. [DUPLICATO — vedi anche: 2026-09-06_18_Slovenia_Primorsko-notranjska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
